--- a/downloads/Packing and Invoice Summery.xlsx
+++ b/downloads/Packing and Invoice Summery.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="44">
   <si>
     <t>DATE</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>16-Aug-2025</t>
+  </si>
+  <si>
+    <t>17-Aug-2025</t>
   </si>
 </sst>
 </file>
@@ -553,7 +556,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -2181,42 +2184,50 @@
         <v>26</v>
       </c>
       <c r="C32" s="2">
-        <v>137415</v>
+        <v>291863</v>
       </c>
       <c r="D32" s="2">
-        <v>6716</v>
-      </c>
-      <c r="E32" s="2"/>
+        <v>14130</v>
+      </c>
+      <c r="E32" s="2">
+        <v>5475</v>
+      </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2">
-        <v>976</v>
+        <v>7154</v>
       </c>
       <c r="L32" s="2">
-        <v>700</v>
+        <v>30000</v>
       </c>
       <c r="M32" s="2">
-        <v>59268</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>232992</v>
+      </c>
+      <c r="N32" s="2">
+        <v>9138</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
+      <c r="Q32" s="2">
+        <v>320</v>
+      </c>
       <c r="R32" s="2">
-        <v>2651</v>
+        <v>8523</v>
       </c>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2">
-        <v>318</v>
+        <v>10256</v>
       </c>
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
+      <c r="Y32" s="2">
+        <v>405125</v>
+      </c>
       <c r="Z32" s="2">
         <f>SUM(C32:X32)</f>
         <v>0</v>
@@ -2228,42 +2239,50 @@
         <v>27</v>
       </c>
       <c r="C33" s="3">
-        <v>14522.0769</v>
+        <v>30087.59360000002</v>
       </c>
       <c r="D33" s="3">
-        <v>1566.8428</v>
-      </c>
-      <c r="E33" s="3"/>
+        <v>3237.2294</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2190</v>
+      </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3">
-        <v>195.2</v>
+        <v>1430.8</v>
       </c>
       <c r="L33" s="3">
-        <v>91</v>
+        <v>4334.597</v>
       </c>
       <c r="M33" s="3">
-        <v>4755.498999999998</v>
-      </c>
-      <c r="N33" s="3"/>
+        <v>17822.3296</v>
+      </c>
+      <c r="N33" s="3">
+        <v>1317.045</v>
+      </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
+      <c r="Q33" s="3">
+        <v>44.8</v>
+      </c>
       <c r="R33" s="3">
-        <v>689.2600000000001</v>
+        <v>2214.112</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3">
-        <v>66.78</v>
+        <v>2188.535</v>
       </c>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
+      <c r="Y33" s="3">
+        <v>582.375</v>
+      </c>
       <c r="Z33" s="3">
         <f>SUM(C33:X33)</f>
         <v>0</v>
@@ -2271,134 +2290,234 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="4">
-        <v>2757270</v>
-      </c>
-      <c r="D34" s="4">
-        <v>212564</v>
-      </c>
-      <c r="E34" s="4">
-        <v>57462</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4">
-        <v>36191</v>
-      </c>
-      <c r="L34" s="4">
-        <v>595272</v>
-      </c>
-      <c r="M34" s="4">
-        <v>2336654</v>
-      </c>
-      <c r="N34" s="4">
-        <v>50235</v>
-      </c>
-      <c r="O34" s="4">
-        <v>3000</v>
-      </c>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4">
-        <v>30466</v>
-      </c>
-      <c r="R34" s="4">
-        <v>104908</v>
-      </c>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4">
-        <v>5950</v>
-      </c>
-      <c r="U34" s="4">
-        <v>11469</v>
-      </c>
-      <c r="V34" s="4">
-        <v>89975</v>
-      </c>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4">
-        <v>4000</v>
-      </c>
-      <c r="Y34" s="4">
-        <v>1412723</v>
-      </c>
-      <c r="Z34" s="4">
+      <c r="C34" s="2">
+        <v>68773</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1871</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1643</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2">
+        <v>1763</v>
+      </c>
+      <c r="L34" s="2">
+        <v>7370</v>
+      </c>
+      <c r="M34" s="2">
+        <v>106187</v>
+      </c>
+      <c r="N34" s="2">
+        <v>6044</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2">
+        <v>324</v>
+      </c>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2">
         <f>SUM(C34:X34)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:26">
       <c r="A35" s="1"/>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="6">
-        <v>277625</v>
-      </c>
-      <c r="D35" s="6">
-        <v>40493</v>
-      </c>
-      <c r="E35" s="6">
-        <v>27489</v>
-      </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="6">
-        <v>7238</v>
-      </c>
-      <c r="L35" s="6">
-        <v>83157</v>
-      </c>
-      <c r="M35" s="6">
-        <v>163864</v>
-      </c>
-      <c r="N35" s="6">
-        <v>8738</v>
-      </c>
-      <c r="O35" s="6">
+      <c r="C35" s="3">
+        <v>7451.204500000003</v>
+      </c>
+      <c r="D35" s="3">
+        <v>436.5043</v>
+      </c>
+      <c r="E35" s="3">
+        <v>657.2</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3">
+        <v>352.6</v>
+      </c>
+      <c r="L35" s="3">
+        <v>973.9825</v>
+      </c>
+      <c r="M35" s="3">
+        <v>6397.726000000001</v>
+      </c>
+      <c r="N35" s="3">
+        <v>838.3200000000001</v>
+      </c>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="3"/>
+      <c r="V35" s="3">
+        <v>84.13499999999999</v>
+      </c>
+      <c r="W35" s="3"/>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3">
+        <f>SUM(C35:X35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26">
+      <c r="A36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="4">
+        <v>2980491</v>
+      </c>
+      <c r="D36" s="4">
+        <v>221849</v>
+      </c>
+      <c r="E36" s="4">
+        <v>64580</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4">
+        <v>44132</v>
+      </c>
+      <c r="L36" s="4">
+        <v>631942</v>
+      </c>
+      <c r="M36" s="4">
+        <v>2616565</v>
+      </c>
+      <c r="N36" s="4">
+        <v>65417</v>
+      </c>
+      <c r="O36" s="4">
+        <v>3000</v>
+      </c>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4">
+        <v>30786</v>
+      </c>
+      <c r="R36" s="4">
+        <v>110780</v>
+      </c>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4">
+        <v>5950</v>
+      </c>
+      <c r="U36" s="4">
+        <v>11469</v>
+      </c>
+      <c r="V36" s="4">
+        <v>100237</v>
+      </c>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4">
+        <v>4000</v>
+      </c>
+      <c r="Y36" s="4">
+        <v>1817848</v>
+      </c>
+      <c r="Z36" s="4">
+        <f>SUM(C36:X36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26">
+      <c r="A37" s="1"/>
+      <c r="B37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="6">
+        <v>300642</v>
+      </c>
+      <c r="D37" s="6">
+        <v>42600</v>
+      </c>
+      <c r="E37" s="6">
+        <v>30336</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="6">
+        <v>8826</v>
+      </c>
+      <c r="L37" s="6">
+        <v>88375</v>
+      </c>
+      <c r="M37" s="6">
+        <v>183329</v>
+      </c>
+      <c r="N37" s="6">
+        <v>10893</v>
+      </c>
+      <c r="O37" s="6">
         <v>744</v>
       </c>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="6">
-        <v>5571</v>
-      </c>
-      <c r="R35" s="6">
-        <v>27492</v>
-      </c>
-      <c r="S35" s="4"/>
-      <c r="T35" s="6">
+      <c r="P37" s="4"/>
+      <c r="Q37" s="6">
+        <v>5616</v>
+      </c>
+      <c r="R37" s="6">
+        <v>29017</v>
+      </c>
+      <c r="S37" s="4"/>
+      <c r="T37" s="6">
         <v>961</v>
       </c>
-      <c r="U35" s="6">
+      <c r="U37" s="6">
         <v>1317</v>
       </c>
-      <c r="V35" s="6">
-        <v>18378</v>
-      </c>
-      <c r="W35" s="4"/>
-      <c r="X35" s="6">
+      <c r="V37" s="6">
+        <v>20584</v>
+      </c>
+      <c r="W37" s="4"/>
+      <c r="X37" s="6">
         <v>2494</v>
       </c>
-      <c r="Y35" s="6">
-        <v>71626</v>
-      </c>
-      <c r="Z35" s="6">
-        <f>SUM(C35:X35)</f>
+      <c r="Y37" s="6">
+        <v>72209</v>
+      </c>
+      <c r="Z37" s="6">
+        <f>SUM(C37:X37)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="41">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -2416,29 +2535,30 @@
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A36:A37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="portrait"/>
